--- a/data/daily/2026-10/2026-10-08.xlsx
+++ b/data/daily/2026-10/2026-10-08.xlsx
@@ -11,9 +11,7 @@
     <sheet name="카카오선물하기_카드형" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="다이소몰" sheetId="3" state="hidden" r:id="rId3"/>
     <sheet name="다이소몰_카드형" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="올리브영" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet name="올리브영_카드형" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="카테고리통계" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="올리브영" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1170,14 +1168,39 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1192,17 +1215,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>3</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1240,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,160 +1290,110 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="323850" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1425,27 +1423,52 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1453,204 +1476,179 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="866775" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1906,261 +1904,6 @@
       <rowOff>0</rowOff>
     </from>
     <ext cx="457200" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2596,21 +2339,21 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16233</v>
+        <v>16236</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>피로 해소 및 활력 충전 — 복용 후 지친 몸에 에너지가 돌고 활력이 생김</t>
+          <t>피로 회복 및 활력 증진 — 복용 시 피로가 해소되고 활력이 생겨 피곤할 때 꺼내먹기 좋음</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>선물용으로 높은 만족도 — 고급스러운 구성으로 생일 등 지인 선물 시 만족도가 높음</t>
+          <t>증정 티백의 우수한 품질 — 사은품으로 제공된 차의 향이 매우 훌륭함</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>섭취 편의성과 좋은 맛 — 액상과 정제가 함께 있어 물 없이도 간편하고 맛있게 섭취 가능함</t>
+          <t>빠른 배송과 선물 만족도 — 배송이 빠르고 선물용으로 주고받기에 매우 만족스러움</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -2655,21 +2398,21 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15540</v>
+        <v>15545</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>피로 개선 및 활력 충전 — 섭취한 날과 안 마신 날의 컨디션 차이가 확실하며 에너지 보충에 도움됨</t>
+          <t>피로 개선 및 에너지 충전 — 복용 시 체력과 집중력 향상에 도움이 됨</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>간편한 일체형 휴대성 — 정제와 액상이 한 병에 들어 있어 외출 시 물 없이 간편하게 복용 가능함</t>
+          <t>휴대 및 섭취의 편의성 — 알약과 액상이 함께 구성되어 한 손에 들어오며 휴대와 섭취가 간편함</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>깔끔한 패키지와 선물 만족도 — 포장이 고급스럽고 배송이 빨라 지인 생일 선물용으로 인기가 높음</t>
+          <t>고급스러운 선물용 구성 — 포장이 고급스럽고 배송이 빨라 선물용으로 적합함</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -2718,22 +2461,18 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>피로 회복 및 기운 충전 — 복용 후 다음 날 피로가 덜하고 몸에 활력이 생기는 것을 체감함</t>
+          <t>우수한 피로 회복 효과 — 복용 후 활력이 생기고 피로감이 줄어드는 것을 체감함</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>정성스러운 안심 포장 — 포장이 꼼꼼하고 고급스럽게 배송되어 선물 받거나 줄 때 만족스러움</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>진한 액상 영양 성분 — 일반적인 액상 비타민 대비 농도가 진하여 효과가 뛰어난 느낌을 줌</t>
-        </is>
-      </c>
+          <t>꼼꼼한 포장과 선물 만족 — 배송 포장이 꼼꼼하며 선물용으로 이용하기에 좋음</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>액상 특유의 아쉬운 맛 — 액상 비타민 제형 특유의 맛 자체는 아쉽다는 반응이 있음</t>
+          <t>액상 제형의 아쉬운 맛 — 맛 자체는 아주 뛰어나지 않으나 타 액상 비타민 대비 진함</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -2781,17 +2520,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>맛있는 젤리 형태 섭취 — 간식처럼 쫄깃하고 달콤하여 약 먹는 부담 없이 즐겁게 섭취함</t>
+          <t>맛있는 젤리 형태 제형 — 탱글하고 맛있는 젤리 형태라 거부감 없이 복용 가능함</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>정제 대비 편한 목넘김 — 큰 알약을 삼키기 어려워하는 사람도 거부감 없이 매일 챙겨 먹기 편함</t>
+          <t>간편한 영양 섭취 방식 — 알약을 잘 못 먹는 사람도 간식처럼 매일 쉽게 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>귀여운 패키지와 굿즈 — 감귤 형태의 귀여운 손잡이 케이스와 동봉된 키캡에 대한 만족도가 높음</t>
+          <t>귀여운 패키지 및 굿즈 — 감귤 모양의 귀여운 패키지와 증정품 키캡의 만족도가 높음</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -2840,22 +2579,22 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 체감 — 출근길이나 교대 근무 중 복용 시 덜 피곤하고 활력이 충전됨</t>
+          <t>효과적인 피로 개선 — 복용 시 피로가 줄어들고 에너지 충전에 도움이 됨</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>간편한 휴대 및 목넘김 — 한 병씩 들고 다니며 마실 수 있고 목넘김이 부드러워 섭취가 쉬움</t>
+          <t>편안한 섭취 및 휴대성 — 마시는 형태라 섭취가 간편하고 들고 다니기 쉬움</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>부담 없는 합리적 가격 — 타사 이뮨 비타민 대비 저렴한 가격대로 구매 및 선물하기 좋음</t>
+          <t>합리적인 가격대 — 가격이 저렴하여 가성비가 우수함</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>단품 박스 배송의 아쉬움 — 쇼핑백 없이 택배 박스에 본품만 바로 담겨 배송되어 아쉬움이 있음</t>
+          <t>선물용 포장재 미흡 — 쇼핑백 없이 박스째 배송되어 선물용 포장이 다소 당황스러움</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -2903,24 +2642,20 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>기력 회복 및 아침 컨디션 — 취침 전이나 피로할 때 섭취하면 다음 날 아침 컨디션 회복에 도움됨</t>
+          <t>기력 회복 및 피로 개선 — 취침 전 복용 시 아침 컨디션이 달라지고 기력 회복에 좋음</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>알찬 증정 구성과 패키지 — 본품 외 2입 추가 증정 혜택이 있고 깔끔한 선물용 패키지를 갖춤</t>
+          <t>깔끔한 패키지와 구성 — 단독 에디션 패키지가 깔끔하며 증정 구성이 알참</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>올인원 복합 섭취 편의 — 정제와 액상이 함께 구성되어 여러 영양제를 따로 챙길 필요가 없음</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>다소 아쉬운 단일 용량 — 소포장 구성으로 인해 선물의 외관상 부피감이 다소 아쉽게 느껴질 수 있음</t>
-        </is>
-      </c>
+          <t>간편한 올인원 복용 — 알약과 음료가 함께 있어 따로 영양제를 챙길 필요 없이 간편함</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
@@ -2966,17 +2701,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>고급스러운 명절 에디션 — 쇼핑백과 전용 상자 포장이 고급스러워 귀한 명절 선물용으로 제격임</t>
+          <t>고급스러운 포장 디자인 — 고급진 박스와 종이가방 구성으로 명절 선물용으로 적합함</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>휴대성 높은 개별 병 포장 — 하루 한 병씩 가볍게 챙겨 출근할 수 있어 복용이 간편함</t>
+          <t>간편한 섭취 및 휴대성 — 개별 병 포장으로 출근 시 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>환절기 면역 및 체력 관리 — 체력이 떨어지거나 환절기 감기 예방을 위한 영양 보충용으로 만족함</t>
+          <t>환절기 면역력 강화 — 복용 시 피로 충전 및 환절기 면역력 관리에 도움 됨</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -3025,17 +2760,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>피로 완화와 컨디션 회복 — 꾸준히 복용한 후 몸이 한결 덜 피곤하고 기운이 솟는 느낌을 받음</t>
+          <t>신기한 포장과 뛰어난 맛 — 액상과 분말이 결합된 신기한 제형으로 맛이 좋음</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>맛있고 신기한 제형 구성 — 액상과 분말이 결합된 독특한 형태이며 맛이 좋아 부담 없이 먹힘</t>
+          <t>피로 개선 및 활력 충전 — 복용 시 피로감이 줄고 몸의 컨디션이 개선됨</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>센스 있는 건강 선물 — 포장이 깔끔하고 브랜드 신뢰도가 높아 감기나 생일 응원 선물로 만족함</t>
+          <t>빠른 배송과 간편한 섭취 — 배송이 빠르고 간편하게 섭취할 수 있음</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -3084,17 +2819,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>성별 맞춤형 영양 설계 — 남성과 여성용 옵션을 선택할 수 있어 받는 사람에게 맞춤 선물이 가능함</t>
+          <t>성별 맞춤 제품 옵션 — 남성과 여성용 선택이 가능하여 영양 성분 구성이 우수함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>직장인 맞춤 에너지 부스터 — 섭취 시 피로감이 줄어들고 업무 중 활력을 끌어올리는 데 유용함</t>
+          <t>거부감 없는 맛과 편리성 — 쓴맛이 없고 휴대 및 복용이 간편함</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>쓰지 않고 편안한 목넘김 — 비타민 특유의 쓴맛이 없고 농도가 진득하여 간편하게 복용 가능함</t>
+          <t>훌륭한 피로 회복 효과 — 직장인 활력 증진 및 피로 회복에 탁월함</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -3143,27 +2878,23 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>고함량 비타민C 체감 효과 — 고용량 비타민C 보충을 통해 피부 및 일상 컨디션 유지에 도움을 줌</t>
+          <t>고함량 영국산 비타민C — 3000mg 고용량에 영국산 원료를 사용하여 신뢰도가 높음</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>영국산 원료의 높은 신뢰도 — 신뢰할 수 있는 브랜드와 영국산 원산지 원료를 사용하여 꾸준히 구매함</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>호불호 적은 건강 선물 — 호불호가 크지 않은 필수 영양소라 지인 생일 선물용으로 추천됨</t>
-        </is>
-      </c>
+          <t>피부 및 컨디션 개선 — 꾸준히 복용 시 피부와 몸의 컨디션 유지에 도움이 됨</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>강한 신맛과 분말 불호 — 분말 특유의 맛이 매우 시고 먹기 힘들어 섭취가 처치 곤란하게 느껴짐</t>
+          <t>부담스러운 분말 맛 — 분말 특유의 시고 강한 맛 때문에 먹기 힘들 수 있음</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>캡슐 제형의 미제공 — 가루 섭취가 불편하여 캡슐 형태의 제품을 원하는 소비자 의견이 있음</t>
+          <t>캡슐 제형의 부재 — 분말 제형이라 캡슐형 제품을 선호하는 사용자에게 아쉬움</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -3206,28 +2937,24 @@
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>아이돌 굿즈와 알찬 세트 — 포토카드 및 단백질바 증정 이벤트로 팬심과 실용성을 동시에 만족시킴</t>
+          <t>만족스러운 굿즈 구성 — 포토카드, 엽서, 단백질바 등 사은품 구성이 알차고 예쁨</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>텁텁함 없는 달콤한 풍미 — 소다 아이스크림 맛으로 입자가 곱고 입안이 텁텁하지 않아 맛있게 먹힘</t>
+          <t>우수한 소화 개선 도움 — 복용 후 소화가 원활해지고 속이 편안해짐</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>식후 편안한 소화감 — 복용 후 속이 더부룩하지 않고 소화가 원활하게 이루어짐을 경험함</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>일시적인 배송 지연 — 특정 주문 기간에 따라 배송이 다소 늦어지는 경우가 발생함</t>
-        </is>
-      </c>
+          <t>맛있는 맛과 고운 입자 — 입자가 고와 텁텁하지 않고 달콤한 맛이 남</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
     </row>
@@ -3273,24 +3000,20 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>밀가루 섭취 후 속 편안함 — 소화가 잘 안 되거나 밀가루 음식을 먹은 뒤 섭취 시 속이 편안해짐</t>
+          <t>편안한 소화 및 속 개선 — 밀가루 음식 섭취 후 복용 시 소화를 돕고 속이 편해짐</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>구수한 고구마 곡물 맛 — 거부감 없는 구수한 고구마 풍미로 가족 모두 부담 없이 섭취 가능함</t>
+          <t>구수한 고구마 맛 — 구수한 고구마 맛이 나 부담 없이 먹을 수 있음</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>풍성한 사은품 및 추가 증정 — 파인키위효소, 고단백질바 등 증정품 구성이 다양하고 만족스러움</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>가격 부담 및 할인 희망 — 정기적으로 구매해 먹기에는 다소 부담스러워 추가 할인을 바라는 의견이 있음</t>
-        </is>
-      </c>
+          <t>푸짐한 추가 사은품 — 곡물바 등 다양한 사은품 증정 구성이 만족스러움</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
     </row>
@@ -3336,22 +3059,18 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>고급스러운 포장과 플리츠백 — 오간자 패키지와 가방 세트 구성이 매우 예뻐 개봉 시 감동을 줌</t>
+          <t>고급스럽고 예쁜 패키징 — 플리츠백과 오간자 포장이 화려하고 예뻐 선물 만족도가 높음</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>비린 맛 없는 맛있는 앰플 — 콜라겐 특유의 비린 느낌 없이 맛있게 하루 한 병씩 마시기 편함</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>피부 탄력 및 피로 완화 — 섭취 후 피로감이 덜하고 피부 탄력 개선에 대한 기대감이 높음</t>
-        </is>
-      </c>
+          <t>맛있는 맛과 피로 개선 — 음용하기에 맛이 좋고 복용 후 피로가 덜함</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>다소 높은 가격대 부담 — 제품 단가가 다소 비싸 할인 혜택이 있을 때만 구매하게 됨</t>
+          <t>다소 높은 정가 가격 — 가격대가 높아 할인 행사 시 구매를 선호하게 됨</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -3399,22 +3118,22 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>촉촉하고 부드러운 육질 — 닭가슴살 특유의 퍽퍽함 없이 촉촉하고 부드러운 식감을 유지함</t>
+          <t>촉촉하고 맛있는 소스 — 닭가슴살 잡내 없이 촉촉하며 소스가 다양하고 맛있음</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>질리지 않는 다채로운 양념 — 떡볶이맛, 소스 닭가슴살 등 소스 종류가 다양해 식단 관리가 수월함</t>
+          <t>우수한 가성비 및 구성 — 다양한 구성의 단백질 식단을 저렴하게 구매 가능함</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>훌륭한 가성비와 식사 대용 — 할인 시 가격이 매우 합리적이며 기숙사나 간식 대용으로 든든함</t>
+          <t>빠르고 안전한 배송 — 배송이 빠르고 튼튼하게 전달됨</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>그릴 제품 누락의 아쉬움 — 세트 구성에 선호도가 높은 파우치형 그릴 제품이 빠져 아쉬워함</t>
+          <t>특정 인기 구성의 부재 — 선호도가 높은 파우치형 그릴 제품이 구성에 포함되지 않음</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
@@ -3423,7 +3142,7 @@
     <row r="16" ht="38" customHeight="1">
       <c r="B16" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -3431,62 +3150,58 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
+          <t>[혼합 18개입] 셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나+2팩</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>셀렉스</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>23,900원</t>
+          <t>31,900원</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180362</t>
+          <t>https://gift.kakao.com/product/13550266</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260911094744_fdcb15f83b684390b6fd43416e90d400.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260907094509_48a662610e174029823081c612ed4755.jpg</t>
         </is>
       </c>
       <c r="I16" t="n">
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>906</v>
+        <v>218</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>소화 불량 및 더부룩함 완화 — 식후 섭취 시 속이 편안해지고 가벼워지는 느낌을 꾸준히 체감함</t>
+          <t>비린맛 없는 맛있는 음료 — 단백질 음료 특유의 비리고 텁텁한 맛이 전혀 없음</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>만족스러운 사은품 증정 — 10포 추가 증정과 파로저당씬칩 등 사은품 혜택이 풍성하게 제공됨</t>
+          <t>포만감 및 영양 공급 — 운동 후 마시면 포만감이 생기고 득근에 도움 됨</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>부담 없이 편안한 맛 — 맛이 거북하지 않고 고소하여 어르신들도 즐겨 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>이전 구매 대비 맛 변화 — 과거에 구매해 먹었을 때와 비교해 맛이 다소 다르게 느껴진다는 평이 있음</t>
-        </is>
-      </c>
+          <t>빠른 배송과 추가 증정 — 배송이 빠르고 서비스 팩이 동봉되어 만족스러움</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
     </row>
     <row r="17" ht="38" customHeight="1">
       <c r="B17" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -3494,12 +3209,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[선물/운동]삼대오백 필수 아미노산 EAA 300g 헬스 직장인 수분보충</t>
+          <t>쇼핑백 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>삼대오백</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3509,43 +3224,47 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10908258</t>
+          <t>https://gift.kakao.com/product/7556791</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261007162359_e049ea90261c452fae5a5a6f6ff7e802.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>1177</v>
+        <v>1535</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>음료수처럼 뛰어난 풍미 — 요구르트맛, 알로에맛, 매실맛 등 맛이 매우 뛰어나 음료 대용으로 마심</t>
+          <t>아르기닌과 밀크씨슬 구성 — 활력 충전과 간 건강을 함께 챙겨 피로 회복에 효과적임</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>운동 수행력과 집중력 향상 — 운동 중 수분 및 전해질 공급이 원활하여 운동 집중력이 좋아짐</t>
+          <t>선물용 쇼핑백 제공 — 쇼핑백이 함께 포함되어 선물용으로 깔끔함</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>넉넉한 용량 대비 가성비 — 오랜 기간 섭취할 수 있을 만큼 대용량으로 가격 대비 효율이 우수함</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>넉넉한 2개월분 용량 — 2개월 동안 여유 있게 복용 가능함</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>증정 쇼핑백 부속 누락 — 동봉된 쇼핑백의 끈이 달리지 않은 상태로 배송됨</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
     </row>
     <row r="18" ht="38" customHeight="1">
       <c r="B18" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -3553,53 +3272,53 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>쇼핑백 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>27,900원</t>
+          <t>33,200원</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7556791</t>
+          <t>https://gift.kakao.com/product/12064702</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
         </is>
       </c>
       <c r="I18" t="n">
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>1535</v>
+        <v>21</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>아침 피로 감소 체감 — 기상 시 몸이 가볍고 일상 및 운동 시 지치지 않는 체력을 유지함</t>
+          <t>확실한 숙취 해소 효과 — 음주 전후 섭취 시 다음 날 숙취와 피로감이 줄어듦</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>아르기닌과 밀크씨슬 복합 — 활력과 간 건강을 동시에 챙길 수 있는 필수 조합으로 구성이 알참</t>
+          <t>고급스러운 선물용 패키지 — 보라색 박스와 쇼핑백 형태 포장이 고급스러움</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>쇼핑백 동봉 선물 적합성 — 전용 쇼핑백이 함께 제공되어 직장 동료나 지인 선물용으로 전달하기 편함</t>
+          <t>휴대가 편한 개별 스틱 — 개별 스틱 포장이라 외출 시 지참하기 수월함</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>쇼핑백 동봉 불량 발생 — 선물용으로 주문했으나 쇼핑백 손잡이 끈이 누락되어 배송된 사례가 있음</t>
+          <t>한약 맛에 대한 호불호 — 쌍화탕이나 한약재 풍미가 느껴져 입맛에 따른 호불호 존재함</t>
         </is>
       </c>
       <c r="O18" t="inlineStr"/>
@@ -3608,7 +3327,7 @@
     <row r="19" ht="38" customHeight="1">
       <c r="B19" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -3616,53 +3335,49 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[한끼통살] 닭가슴살 순삭 10팩세트(소스통살5+닭가슴살볼5)</t>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>31,500원</t>
+          <t>23,900원</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10848340</t>
+          <t>https://gift.kakao.com/product/13180362</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20241128105752_bb00bdfb255b4aad91bbff59ec2c2cfd.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260911094744_fdcb15f83b684390b6fd43416e90d400.jpg</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>69</v>
+        <v>906</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>퍽퍽하지 않은 촉촉한 식감 — 전자레인지 조리 후에도 살이 퍽퍽하지 않고 쫄깃하며 부드러움</t>
+          <t>소화 및 장 건강 개선 — 복용 후 속이 편안해지며 소화와 변비 개선에 도움이 됨</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>전자레인지 간편 조리 — 해동 후 데우기만 하면 바로 먹을 수 있어 바쁜 아침 식단으로 편리함</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>한입 크기 볼 형태 편리성 — 닭가슴살볼이 한입 크기로 되어 있어 샐러드나 도시락 반찬으로 곁들이기 좋음</t>
-        </is>
-      </c>
+          <t>저렴한 가격 및 사은품 — 가격이 저렴하고 추가 사은품 구성이 풍성함</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>다소 느린 배송 처리 — 주문 후 수령까지 배송 속도가 다소 느리게 느껴졌다는 반응이 있음</t>
+          <t>제품 맛의 차이 발생 — 이전 구매 시와 비교했을 때 맛에 약간의 차이가 느껴짐</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
@@ -3679,55 +3394,51 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+          <t>[선물/운동]삼대오백 필수 아미노산 EAA 300g 헬스 직장인 수분보충</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>알디콤</t>
+          <t>삼대오백</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>33,200원</t>
+          <t>27,900원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12064702</t>
+          <t>https://gift.kakao.com/product/10908258</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261007162359_e049ea90261c452fae5a5a6f6ff7e802.jpg</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>21</v>
+        <v>1177</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>음주 다음 날 숙취 완화 — 음주 전후 섭취 시 아침 특유의 처짐과 두통 등 숙취가 현저히 덜함</t>
+          <t>맛이 뛰어난 다양한 종류 — 매실, 요구르트, 알로에 등 다양한 맛이 매우 훌륭함</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>간편한 스틱형 개별 포장 — 주머니나 가방에 쏙 들어가는 작은 파우치형이라 술자리에 지참하기 용이함</t>
+          <t>운동 수행 능력 향상 — 운동 시 수분 및 전해질 보충으로 수행 능력과 집중력이 향상됨</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>고급스러운 리본 선물 포장 — 보라색 쇼핑백 패키지로 제작되어 애주가 지인에게 선물하기 좋음</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>한약 및 약재 특유의 향미 — 쌍화탕이나 한약 느낌의 쓴맛이 감돌아 약재 향을 싫어하는 경우 호불호가 갈림</t>
-        </is>
-      </c>
+          <t>대용량의 높은 가성비 — 용량이 넉넉하여 오랫동안 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
     </row>
@@ -3773,22 +3484,22 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>아침 모닝 부스터 효과 — 졸린 눈이 번쩍 뜨이고 몸이 따뜻해지며 하루 에너지를 채워줌</t>
+          <t>상큼하고 맛있는 맛 — 과일 성분이 함께 들어있어 생강 맛이 상큼하고 부담 없음</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>상큼하고 부담 없는 풍미 — 생강 함량이 높지만 과일 주스가 블렌딩되어 달콤 쌉싸름하게 맛있음</t>
+          <t>활력 충전 및 온기 전달 — 공복 복용 시 몸이 따뜻해지고 아침 활력 충전에 도움이 됨</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>귀여운 병과 메시지 증정 — 미니 보틀 형태의 병이 귀엽고 의미가 좋아 지인 응원 선물로 적합함</t>
+          <t>귀여운 미니 보틀 디자인 — 용기 디자인이 귀여워 손이 자주 감</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>아이 및 가족의 섭취 거부 — 특유의 톡 쏘는 생강 맛이 강해 어린이나 일부 가족 구성원이 먹기 어려워함</t>
+          <t>생강 특유의 강한 맛 — 생강 특유의 톡 쏘는 맛으로 인해 사람에 따라 거부감을 느낄 수 있음</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
@@ -4112,10 +3823,10 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16233</v>
+        <v>16236</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15540</v>
+        <v>15545</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>3400</v>
@@ -4150,72 +3861,70 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>피로 해소 및 활력 충전 — 복용 후 지친 몸에 에너지가 돌고 활력이 생김
-선물용으로 높은 만족도 — 고급스러운 구성으로 생일 등 지인 선물 시 만족도가 높음
-섭취 편의성과 좋은 맛 — 액상과 정제가 함께 있어 물 없이도 간편하고 맛있게 섭취 가능함</t>
+          <t>피로 회복 및 활력 증진 — 복용 시 피로가 해소되고 활력이 생겨 피곤할 때 꺼내먹기 좋음
+증정 티백의 우수한 품질 — 사은품으로 제공된 차의 향이 매우 훌륭함
+빠른 배송과 선물 만족도 — 배송이 빠르고 선물용으로 주고받기에 매우 만족스러움</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>피로 개선 및 활력 충전 — 섭취한 날과 안 마신 날의 컨디션 차이가 확실하며 에너지 보충에 도움됨
-간편한 일체형 휴대성 — 정제와 액상이 한 병에 들어 있어 외출 시 물 없이 간편하게 복용 가능함
-깔끔한 패키지와 선물 만족도 — 포장이 고급스럽고 배송이 빨라 지인 생일 선물용으로 인기가 높음</t>
+          <t>피로 개선 및 에너지 충전 — 복용 시 체력과 집중력 향상에 도움이 됨
+휴대 및 섭취의 편의성 — 알약과 액상이 함께 구성되어 한 손에 들어오며 휴대와 섭취가 간편함
+고급스러운 선물용 구성 — 포장이 고급스럽고 배송이 빨라 선물용으로 적합함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>피로 회복 및 기운 충전 — 복용 후 다음 날 피로가 덜하고 몸에 활력이 생기는 것을 체감함
-정성스러운 안심 포장 — 포장이 꼼꼼하고 고급스럽게 배송되어 선물 받거나 줄 때 만족스러움
-진한 액상 영양 성분 — 일반적인 액상 비타민 대비 농도가 진하여 효과가 뛰어난 느낌을 줌</t>
+          <t>우수한 피로 회복 효과 — 복용 후 활력이 생기고 피로감이 줄어드는 것을 체감함
+꼼꼼한 포장과 선물 만족 — 배송 포장이 꼼꼼하며 선물용으로 이용하기에 좋음</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 젤리 형태 섭취 — 간식처럼 쫄깃하고 달콤하여 약 먹는 부담 없이 즐겁게 섭취함
-정제 대비 편한 목넘김 — 큰 알약을 삼키기 어려워하는 사람도 거부감 없이 매일 챙겨 먹기 편함
-귀여운 패키지와 굿즈 — 감귤 형태의 귀여운 손잡이 케이스와 동봉된 키캡에 대한 만족도가 높음</t>
+          <t>맛있는 젤리 형태 제형 — 탱글하고 맛있는 젤리 형태라 거부감 없이 복용 가능함
+간편한 영양 섭취 방식 — 알약을 잘 못 먹는 사람도 간식처럼 매일 쉽게 챙겨 먹기 좋음
+귀여운 패키지 및 굿즈 — 감귤 모양의 귀여운 패키지와 증정품 키캡의 만족도가 높음</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 체감 — 출근길이나 교대 근무 중 복용 시 덜 피곤하고 활력이 충전됨
-간편한 휴대 및 목넘김 — 한 병씩 들고 다니며 마실 수 있고 목넘김이 부드러워 섭취가 쉬움
-부담 없는 합리적 가격 — 타사 이뮨 비타민 대비 저렴한 가격대로 구매 및 선물하기 좋음</t>
+          <t>효과적인 피로 개선 — 복용 시 피로가 줄어들고 에너지 충전에 도움이 됨
+편안한 섭취 및 휴대성 — 마시는 형태라 섭취가 간편하고 들고 다니기 쉬움
+합리적인 가격대 — 가격이 저렴하여 가성비가 우수함</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>기력 회복 및 아침 컨디션 — 취침 전이나 피로할 때 섭취하면 다음 날 아침 컨디션 회복에 도움됨
-알찬 증정 구성과 패키지 — 본품 외 2입 추가 증정 혜택이 있고 깔끔한 선물용 패키지를 갖춤
-올인원 복합 섭취 편의 — 정제와 액상이 함께 구성되어 여러 영양제를 따로 챙길 필요가 없음</t>
+          <t>기력 회복 및 피로 개선 — 취침 전 복용 시 아침 컨디션이 달라지고 기력 회복에 좋음
+깔끔한 패키지와 구성 — 단독 에디션 패키지가 깔끔하며 증정 구성이 알참
+간편한 올인원 복용 — 알약과 음료가 함께 있어 따로 영양제를 챙길 필요 없이 간편함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 명절 에디션 — 쇼핑백과 전용 상자 포장이 고급스러워 귀한 명절 선물용으로 제격임
-휴대성 높은 개별 병 포장 — 하루 한 병씩 가볍게 챙겨 출근할 수 있어 복용이 간편함
-환절기 면역 및 체력 관리 — 체력이 떨어지거나 환절기 감기 예방을 위한 영양 보충용으로 만족함</t>
+          <t>고급스러운 포장 디자인 — 고급진 박스와 종이가방 구성으로 명절 선물용으로 적합함
+간편한 섭취 및 휴대성 — 개별 병 포장으로 출근 시 챙겨 먹기 편함
+환절기 면역력 강화 — 복용 시 피로 충전 및 환절기 면역력 관리에 도움 됨</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>피로 완화와 컨디션 회복 — 꾸준히 복용한 후 몸이 한결 덜 피곤하고 기운이 솟는 느낌을 받음
-맛있고 신기한 제형 구성 — 액상과 분말이 결합된 독특한 형태이며 맛이 좋아 부담 없이 먹힘
-센스 있는 건강 선물 — 포장이 깔끔하고 브랜드 신뢰도가 높아 감기나 생일 응원 선물로 만족함</t>
+          <t>신기한 포장과 뛰어난 맛 — 액상과 분말이 결합된 신기한 제형으로 맛이 좋음
+피로 개선 및 활력 충전 — 복용 시 피로감이 줄고 몸의 컨디션이 개선됨
+빠른 배송과 간편한 섭취 — 배송이 빠르고 간편하게 섭취할 수 있음</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>성별 맞춤형 영양 설계 — 남성과 여성용 옵션을 선택할 수 있어 받는 사람에게 맞춤 선물이 가능함
-직장인 맞춤 에너지 부스터 — 섭취 시 피로감이 줄어들고 업무 중 활력을 끌어올리는 데 유용함
-쓰지 않고 편안한 목넘김 — 비타민 특유의 쓴맛이 없고 농도가 진득하여 간편하게 복용 가능함</t>
+          <t>성별 맞춤 제품 옵션 — 남성과 여성용 선택이 가능하여 영양 성분 구성이 우수함
+거부감 없는 맛과 편리성 — 쓴맛이 없고 휴대 및 복용이 간편함
+훌륭한 피로 회복 효과 — 직장인 활력 증진 및 피로 회복에 탁월함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>고함량 비타민C 체감 효과 — 고용량 비타민C 보충을 통해 피부 및 일상 컨디션 유지에 도움을 줌
-영국산 원료의 높은 신뢰도 — 신뢰할 수 있는 브랜드와 영국산 원산지 원료를 사용하여 꾸준히 구매함
-호불호 적은 건강 선물 — 호불호가 크지 않은 필수 영양소라 지인 생일 선물용으로 추천됨</t>
+          <t>고함량 영국산 비타민C — 3000mg 고용량에 영국산 원료를 사용하여 신뢰도가 높음
+피부 및 컨디션 개선 — 꾸준히 복용 시 피부와 몸의 컨디션 유지에 도움이 됨</t>
         </is>
       </c>
     </row>
@@ -4229,27 +3938,23 @@
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>액상 특유의 아쉬운 맛 — 액상 비타민 제형 특유의 맛 자체는 아쉽다는 반응이 있음</t>
+          <t>액상 제형의 아쉬운 맛 — 맛 자체는 아주 뛰어나지 않으나 타 액상 비타민 대비 진함</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>단품 박스 배송의 아쉬움 — 쇼핑백 없이 택배 박스에 본품만 바로 담겨 배송되어 아쉬움이 있음</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>다소 아쉬운 단일 용량 — 소포장 구성으로 인해 선물의 외관상 부피감이 다소 아쉽게 느껴질 수 있음</t>
-        </is>
-      </c>
+          <t>선물용 포장재 미흡 — 쇼핑백 없이 박스째 배송되어 선물용 포장이 다소 당황스러움</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>강한 신맛과 분말 불호 — 분말 특유의 맛이 매우 시고 먹기 힘들어 섭취가 처치 곤란하게 느껴짐
-캡슐 제형의 미제공 — 가루 섭취가 불편하여 캡슐 형태의 제품을 원하는 소비자 의견이 있음</t>
+          <t>부담스러운 분말 맛 — 분말 특유의 시고 강한 맛 때문에 먹기 힘들 수 있음
+캡슐 제형의 부재 — 분말 제형이라 캡슐형 제품을 선호하는 사용자에게 아쉬움</t>
         </is>
       </c>
     </row>
@@ -4469,22 +4174,22 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -4526,27 +4231,27 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
+          <t>셀렉스</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>익스트림</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>알디콤</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
           <t>그레인온</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>삼대오백</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>익스트림</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>한끼통살</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>알디콤</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -4583,27 +4288,27 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
+          <t>[혼합 18개입] 셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나+2팩</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>쇼핑백 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
           <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>[선물/운동]삼대오백 필수 아미노산 EAA 300g 헬스 직장인 수분보충</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>쇼핑백 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>[한끼통살] 닭가슴살 순삭 10팩세트(소스통살5+닭가슴살볼5)</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -4656,7 +4361,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>1691</v>
@@ -4668,19 +4373,19 @@
         <v>64</v>
       </c>
       <c r="G19" s="3" t="n">
+        <v>218</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>1535</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="J19" s="3" t="n">
         <v>906</v>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="K19" s="3" t="n">
         <v>1177</v>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>1535</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>69</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>21</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>13</v>
@@ -4694,72 +4399,70 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>아이돌 굿즈와 알찬 세트 — 포토카드 및 단백질바 증정 이벤트로 팬심과 실용성을 동시에 만족시킴
-텁텁함 없는 달콤한 풍미 — 소다 아이스크림 맛으로 입자가 곱고 입안이 텁텁하지 않아 맛있게 먹힘
-식후 편안한 소화감 — 복용 후 속이 더부룩하지 않고 소화가 원활하게 이루어짐을 경험함</t>
+          <t>만족스러운 굿즈 구성 — 포토카드, 엽서, 단백질바 등 사은품 구성이 알차고 예쁨
+우수한 소화 개선 도움 — 복용 후 소화가 원활해지고 속이 편안해짐
+맛있는 맛과 고운 입자 — 입자가 고와 텁텁하지 않고 달콤한 맛이 남</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>밀가루 섭취 후 속 편안함 — 소화가 잘 안 되거나 밀가루 음식을 먹은 뒤 섭취 시 속이 편안해짐
-구수한 고구마 곡물 맛 — 거부감 없는 구수한 고구마 풍미로 가족 모두 부담 없이 섭취 가능함
-풍성한 사은품 및 추가 증정 — 파인키위효소, 고단백질바 등 증정품 구성이 다양하고 만족스러움</t>
+          <t>편안한 소화 및 속 개선 — 밀가루 음식 섭취 후 복용 시 소화를 돕고 속이 편해짐
+구수한 고구마 맛 — 구수한 고구마 맛이 나 부담 없이 먹을 수 있음
+푸짐한 추가 사은품 — 곡물바 등 다양한 사은품 증정 구성이 만족스러움</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 포장과 플리츠백 — 오간자 패키지와 가방 세트 구성이 매우 예뻐 개봉 시 감동을 줌
-비린 맛 없는 맛있는 앰플 — 콜라겐 특유의 비린 느낌 없이 맛있게 하루 한 병씩 마시기 편함
-피부 탄력 및 피로 완화 — 섭취 후 피로감이 덜하고 피부 탄력 개선에 대한 기대감이 높음</t>
+          <t>고급스럽고 예쁜 패키징 — 플리츠백과 오간자 포장이 화려하고 예뻐 선물 만족도가 높음
+맛있는 맛과 피로 개선 — 음용하기에 맛이 좋고 복용 후 피로가 덜함</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>촉촉하고 부드러운 육질 — 닭가슴살 특유의 퍽퍽함 없이 촉촉하고 부드러운 식감을 유지함
-질리지 않는 다채로운 양념 — 떡볶이맛, 소스 닭가슴살 등 소스 종류가 다양해 식단 관리가 수월함
-훌륭한 가성비와 식사 대용 — 할인 시 가격이 매우 합리적이며 기숙사나 간식 대용으로 든든함</t>
+          <t>촉촉하고 맛있는 소스 — 닭가슴살 잡내 없이 촉촉하며 소스가 다양하고 맛있음
+우수한 가성비 및 구성 — 다양한 구성의 단백질 식단을 저렴하게 구매 가능함
+빠르고 안전한 배송 — 배송이 빠르고 튼튼하게 전달됨</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>소화 불량 및 더부룩함 완화 — 식후 섭취 시 속이 편안해지고 가벼워지는 느낌을 꾸준히 체감함
-만족스러운 사은품 증정 — 10포 추가 증정과 파로저당씬칩 등 사은품 혜택이 풍성하게 제공됨
-부담 없이 편안한 맛 — 맛이 거북하지 않고 고소하여 어르신들도 즐겨 먹기 좋음</t>
+          <t>비린맛 없는 맛있는 음료 — 단백질 음료 특유의 비리고 텁텁한 맛이 전혀 없음
+포만감 및 영양 공급 — 운동 후 마시면 포만감이 생기고 득근에 도움 됨
+빠른 배송과 추가 증정 — 배송이 빠르고 서비스 팩이 동봉되어 만족스러움</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>음료수처럼 뛰어난 풍미 — 요구르트맛, 알로에맛, 매실맛 등 맛이 매우 뛰어나 음료 대용으로 마심
-운동 수행력과 집중력 향상 — 운동 중 수분 및 전해질 공급이 원활하여 운동 집중력이 좋아짐
-넉넉한 용량 대비 가성비 — 오랜 기간 섭취할 수 있을 만큼 대용량으로 가격 대비 효율이 우수함</t>
+          <t>아르기닌과 밀크씨슬 구성 — 활력 충전과 간 건강을 함께 챙겨 피로 회복에 효과적임
+선물용 쇼핑백 제공 — 쇼핑백이 함께 포함되어 선물용으로 깔끔함
+넉넉한 2개월분 용량 — 2개월 동안 여유 있게 복용 가능함</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>아침 피로 감소 체감 — 기상 시 몸이 가볍고 일상 및 운동 시 지치지 않는 체력을 유지함
-아르기닌과 밀크씨슬 복합 — 활력과 간 건강을 동시에 챙길 수 있는 필수 조합으로 구성이 알참
-쇼핑백 동봉 선물 적합성 — 전용 쇼핑백이 함께 제공되어 직장 동료나 지인 선물용으로 전달하기 편함</t>
+          <t>확실한 숙취 해소 효과 — 음주 전후 섭취 시 다음 날 숙취와 피로감이 줄어듦
+고급스러운 선물용 패키지 — 보라색 박스와 쇼핑백 형태 포장이 고급스러움
+휴대가 편한 개별 스틱 — 개별 스틱 포장이라 외출 시 지참하기 수월함</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>퍽퍽하지 않은 촉촉한 식감 — 전자레인지 조리 후에도 살이 퍽퍽하지 않고 쫄깃하며 부드러움
-전자레인지 간편 조리 — 해동 후 데우기만 하면 바로 먹을 수 있어 바쁜 아침 식단으로 편리함
-한입 크기 볼 형태 편리성 — 닭가슴살볼이 한입 크기로 되어 있어 샐러드나 도시락 반찬으로 곁들이기 좋음</t>
+          <t>소화 및 장 건강 개선 — 복용 후 속이 편안해지며 소화와 변비 개선에 도움이 됨
+저렴한 가격 및 사은품 — 가격이 저렴하고 추가 사은품 구성이 풍성함</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>음주 다음 날 숙취 완화 — 음주 전후 섭취 시 아침 특유의 처짐과 두통 등 숙취가 현저히 덜함
-간편한 스틱형 개별 포장 — 주머니나 가방에 쏙 들어가는 작은 파우치형이라 술자리에 지참하기 용이함
-고급스러운 리본 선물 포장 — 보라색 쇼핑백 패키지로 제작되어 애주가 지인에게 선물하기 좋음</t>
+          <t>맛이 뛰어난 다양한 종류 — 매실, 요구르트, 알로에 등 다양한 맛이 매우 훌륭함
+운동 수행 능력 향상 — 운동 시 수분 및 전해질 보충으로 수행 능력과 집중력이 향상됨
+대용량의 높은 가성비 — 용량이 넉넉하여 오랫동안 먹기 좋음</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>아침 모닝 부스터 효과 — 졸린 눈이 번쩍 뜨이고 몸이 따뜻해지며 하루 에너지를 채워줌
-상큼하고 부담 없는 풍미 — 생강 함량이 높지만 과일 주스가 블렌딩되어 달콤 쌉싸름하게 맛있음
-귀여운 병과 메시지 증정 — 미니 보틀 형태의 병이 귀엽고 의미가 좋아 지인 응원 선물로 적합함</t>
+          <t>상큼하고 맛있는 맛 — 과일 성분이 함께 들어있어 생강 맛이 상큼하고 부담 없음
+활력 충전 및 온기 전달 — 공복 복용 시 몸이 따뜻해지고 아침 활력 충전에 도움이 됨
+귀여운 미니 보틀 디자인 — 용기 디자인이 귀여워 손이 자주 감</t>
         </is>
       </c>
     </row>
@@ -4769,50 +4472,38 @@
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>일시적인 배송 지연 — 특정 주문 기간에 따라 배송이 다소 늦어지는 경우가 발생함</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>가격 부담 및 할인 희망 — 정기적으로 구매해 먹기에는 다소 부담스러워 추가 할인을 바라는 의견이 있음</t>
-        </is>
-      </c>
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>다소 높은 가격대 부담 — 제품 단가가 다소 비싸 할인 혜택이 있을 때만 구매하게 됨</t>
+          <t>다소 높은 정가 가격 — 가격대가 높아 할인 행사 시 구매를 선호하게 됨</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>그릴 제품 누락의 아쉬움 — 세트 구성에 선호도가 높은 파우치형 그릴 제품이 빠져 아쉬워함</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>이전 구매 대비 맛 변화 — 과거에 구매해 먹었을 때와 비교해 맛이 다소 다르게 느껴진다는 평이 있음</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr"/>
+          <t>특정 인기 구성의 부재 — 선호도가 높은 파우치형 그릴 제품이 구성에 포함되지 않음</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>증정 쇼핑백 부속 누락 — 동봉된 쇼핑백의 끈이 달리지 않은 상태로 배송됨</t>
+        </is>
+      </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>쇼핑백 동봉 불량 발생 — 선물용으로 주문했으나 쇼핑백 손잡이 끈이 누락되어 배송된 사례가 있음</t>
+          <t>한약 맛에 대한 호불호 — 쌍화탕이나 한약재 풍미가 느껴져 입맛에 따른 호불호 존재함</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>다소 느린 배송 처리 — 주문 후 수령까지 배송 속도가 다소 느리게 느껴졌다는 반응이 있음</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>한약 및 약재 특유의 향미 — 쌍화탕이나 한약 느낌의 쓴맛이 감돌아 약재 향을 싫어하는 경우 호불호가 갈림</t>
-        </is>
-      </c>
+          <t>제품 맛의 차이 발생 — 이전 구매 시와 비교했을 때 맛에 약간의 차이가 느껴짐</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr"/>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>아이 및 가족의 섭취 거부 — 특유의 톡 쏘는 생강 맛이 강해 어린이나 일부 가족 구성원이 먹기 어려워함</t>
+          <t>생강 특유의 강한 맛 — 생강 특유의 톡 쏘는 맛으로 인해 사람에 따라 거부감을 느낄 수 있음</t>
         </is>
       </c>
     </row>
@@ -4844,27 +4535,27 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
+          <t>31,900원</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>27,900원</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>33,200원</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
           <t>23,900원</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>27,900원</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>27,900원</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>31,500원</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>33,200원</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -5059,7 +4750,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -5067,62 +4758,54 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
+          <t>대웅제약 마그네슘 샷 25ml x 5병 5일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000204&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20251121/aHjoRwP9ejVVuu8M0Td4600000204_00_01aHjoRwP9ejVVuu8M0Td4.png</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J2" t="n">
-        <v>2806</v>
+        <v>1451</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>뛰어난 가격 대비 성능 — 저렴한 가격으로 커피 대용 다이어트 음료를 즐길 수 있어 가성비가 높음</t>
+          <t>뛰어난 가성비 — 다이소 제품답게 매우 저렴한 가격에 구매 가능함</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>거부감 없는 커피 대용 맛 — 일반 커피처럼 마시기 좋고 맛이 깔끔하여 일상 속 대체 음료로 적합함</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>간편한 휴대 및 음용 방식 — 포 형태로 제작되어 어디서든 물에 타서 편하게 섭취 가능함</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>즉각적인 체감 효과 미비 — 다이어트 효과가 즉각적으로 체감되지는 않아 지속적인 확인이 필요함</t>
-        </is>
-      </c>
+          <t>액상 제형의 편의성과 맛 — 액체 타입이라 흡수가 잘 되며 맛도 양호함</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5130,12 +4813,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CJ 카무트 곡물과채콤부 화사 효소 10포 10일분</t>
+          <t>유한양행 장건강 생유산균 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CJ웰케어</t>
+          <t>유한양행</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -5145,51 +4828,39 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=139213437&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651649&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260623/2v2CuiCUbhEwDNpboF5B139213437_00_002v2CuiCUbhEwDNpboF5B.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260325/RN6BLb2wWdxkL0nu9aVK600651649_00_00RN6BLb2wWdxkL0nu9aVK.jpg</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>1264</v>
+        <v>1755</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>건강해지는 느낌과 좋은 맛 — 맛이 거북하지 않아 재구매하며 섭취 시 몸이 건강해지는 느낌을 받음</t>
+          <t>작아서 편한 캡슐 제형 — 캡슐 크기가 작아 목넘김이 편리함</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>중장년층 간편 건강 관리 — 50대 이후 필수 곡물 효소를 간편하게 보충할 수 있어 복용이 수월함</t>
+          <t>저렴한 가격과 알찬 구성 — 가성비가 뛰어나고 보관 용기의 밀폐력이 우수함</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>오프라인 구매의 불편함 — 시중 오프라인 매장에서 판매하는 곳이 적어 구매 접근성이 떨어짐</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>적은 용량 구성의 아쉬움 — 10포 소용량으로 구성되어 30포 이상 대용량 제품을 원하는 아쉬움이 있음</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>미미한 단기 효능 체감 — 복용 후 나타나는 소화 관련 효과가 강하게 느껴지지 않는다는 평이 있음</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5197,51 +4868,51 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대웅제약 루테인 30정 30일분</t>
+          <t>[보령약국 X Pantio] [인교진 PICK] 다이어트 컷 올인원 15포 15일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>판티오</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000126&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=033991021&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/u8Kxfk5gV3uvRKBRNTM6600000126_00_00u8Kxfk5gV3uvRKBRNTM6.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260928/FbxeJLkidw2iKLnCp7Pe033991021_00_00FbxeJLkidw2iKLnCp7Pe.jpg</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>4149</v>
+        <v>261</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>극강의 부담 없는 가성비 — 저렴한 가격대로 매일 꾸준히 눈 건강을 관리할 수 있어 만족스러움</t>
+          <t>하루 1포 간편 복용 — 1일 1포 섭취라 관리가 편함</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>운전 등 일상 섭취 편의 — 운전을 자주 하는 환경에서 복용이 간편하여 매일 챙겨 먹기 수월함</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>빠른 배송 및 포장 만족 — 배송이 신속하게 이루어지고 제품 상태가 양호하여 신뢰도가 높음</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>빠른 배송 서비스 — 배송이 빠름</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>단기 체감 효과의 미흡 — 단기 복용으로는 다이어트 효과를 느끼기 어려움</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
@@ -5256,58 +4927,54 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>자연관 이지슬로 엑스트라버진 올리브오일＆레몬 4병</t>
+          <t>종근당 데일리와이즈 밀크씨슬 12정 12일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032627034&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306204&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260810/jotmVom4KndGXbIlPcuj032627034_00_01jotmVom4KndGXbIlPcuj.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260406/RewRRgsZjRVv0Af38IFQ032306204_00_01RewRRgsZjRVv0Af38IFQ.jpg</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>1131</v>
+        <v>318</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>꾸준한 건강 관리 재구매 — 올리브오일과 레몬즙 조합이 좋아 매번 꾸준하게 재구매하여 섭취함</t>
+          <t>부담 없는 저렴한 가격 — 저렴하게 밀크씨슬을 구매할 수 있음</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>신선한 원료 배합 만족도 — 건강에 유익한 엑스트라버진 올리브오일과 레몬즙을 함께 간편히 마실 수 있음</t>
+          <t>지속적인 건강 관리 도움 — 소포장으로 간편하게 구매하여 꾸준히 복용하기 적합함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>너무 강렬한 산미 부담 — 신맛이 지나치게 강해 마실 때마다 먹기 버거워하는 반응이 있음</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5315,12 +4982,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>오브맘 다이어트 홀릭 30포 15일분</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5330,47 +4997,39 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=913624075&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250519/2rLyPRrrXXN6XdvBMjj5913624075_00_002rLyPRrrXXN6XdvBMjj5.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>1060</v>
+        <v>6611</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>간식처럼 맛있는 다이어트 — 다이어트 보조제임에도 맛이 뛰어나 거부감 없이 자꾸 먹게 됨</t>
+          <t>착한 가격의 극강 가성비 — 한 달 분량 오메가3를 매우 저렴하게 구매할 수 있음</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>부담 없는 가성비와 접근성 — 올리브영 대비 저렴한 가격에 구매할 수 있어 필수 아이템으로 추천됨</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>식단 시 심리적 안정감 — 식단 중 챙겨 먹는 것만으로도 체중 관리에 대한 심리적 만족을 제공함</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>즉각적인 감량 효과 미비 — 단기간 섭취로는 즉각적인 체중 감량 변화를 체감하기 어려움</t>
-        </is>
-      </c>
+          <t>말랑한 캡슐의 목넘김 — 캡슐이 말랑말랑하여 목에 걸리지 않음</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5378,12 +5037,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>올비텐 비타팡팡 30포</t>
+          <t>대웅제약 비타민C 30정 30일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>영진약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -5393,43 +5052,39 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=939986472&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000127&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260310/G3FoDs3n7cYqsOkiYbDR939986472_00_01G3FoDs3n7cYqsOkiYbDR.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/V0qSVbLLgSaCWbYWEu73600000127_00_00V0qSVbLLgSaCWbYWEu73.png</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>116</v>
+        <v>2837</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>아이들의 높은 기호도 — 아이가 질리지 않고 좋아하여 매일 비타민을 챙겨 먹이기에 아주 유용함</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>톡톡 터지는 발포 식감 — 입안에서 슈팅스타처럼 팡팡 터지는 독특한 재미가 있어 먹는 즐거움이 큼</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>뛰어난 품질과 가격 만족 — 5천 원이라는 저렴한 가격 대비 품질이 훌륭하여 다량 쟁여두고 먹임</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>뛰어난 가성비 — 가격 대비 품질이 좋아 무난하게 챙겨 먹기 적합함</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>표면 코팅제의 이질감 — 알약 표면의 코팅 느낌이 약간 강하게 느껴짐</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5437,62 +5092,54 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>자연관 스파이크컷 바나바잎＆카테킨 4병</t>
+          <t>대웅제약 마그네슘 10정 10일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032627033&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000270&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260819/2NKz5YxykngJc58J5cja032627033_00_012NKz5YxykngJc58J5cja.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260504/rjUOcdF4xff4PIy7VUYT600000270_00_01rjUOcdF4xff4PIy7VUYT.png</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>359</v>
+        <v>752</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>흡수 빠른 액상형 섭취 — 액상 형태로 되어 있어 흡수가 빠를 것 같고 하루 한 병 마시기 수월함</t>
+          <t>1,000원의 저렴한 소포장 — 10정 소포장이라 가격 부담 없이 테스트용으로 구매하기 좋음</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>식후 간편한 혈당 관리 — 식사 후 바로 섭취하여 건강 및 다이어트 관리에 심리적 도움을 받음</t>
+          <t>근육 뭉침 및 경련 완화 — 눈떨림이나 다리 경련, 근육 뭉침 증상 완화에 도움이 됨</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>단기 섭취 시 효과 불확실 — 단기간 복용으로는 체감 효과를 뚜렷하게 알기 어렵다는 의견이 있음</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>평범한 체감 대비 가격 — 가격 대비 큰 체감 효과 없이 무난한 편이라는 평가가 존재함</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5500,62 +5147,54 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 혈당컷 다이어트 12정 12일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306201&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260406/NBw0phjtTvR7tEfBicGr032306201_00_01NBw0phjtTvR7tEfBicGr.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>1409</v>
+        <v>7100</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>식후 졸림 및 혈당 완화 — 식후 급격하게 찾아오던 식곤증과 혈당 스파이크 현상이 줄어드는 느낌임</t>
+          <t>피로 회복과 항산화 효과 — 복용 시 항산화 체계 관리 및 피로 회복에 도움을 줌</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>휴대성 높은 개별 소분 포장 — 작게 소분되어 있어 외출 시 가방에 챙겨 다니며 식후 복용하기 편함</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>저렴한 가격의 높은 가성비 — 다이소 유통 제품답게 가격이 저렴하여 부담 없이 시도하기 좋음</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>체감 효과에 대한 아쉬움 — 기대하고 구매했으나 뚜렷한 변화를 느끼지 못해 평범하다는 반응이 있음</t>
-        </is>
-      </c>
+          <t>약사 추천 극강 가성비 — 약사들도 추천할 만큼 가성비가 우수함</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5563,12 +5202,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
+          <t>동국제약 이너케어＆유산균 30캡슐</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -5578,35 +5217,31 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000127&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910677&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/V0qSVbLLgSaCWbYWEu73600000127_00_00V0qSVbLLgSaCWbYWEu73.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250829/mBCVgsNacUdX2MZDROO3610910677_00_00mBCVgsNacUdX2MZDROO3.png</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>2833</v>
+        <v>2899</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>압도적인 저렴한 가격대 — 기존 비타민C 제품 대비 가격이 매우 저렴하여 극강의 가성비를 자랑함</t>
+          <t>빠른 질 분비물 개선 효과 — 단기간 복용에도 질 분비물이 줄어드는 개선 효과를 체감함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>간편한 일상 면역력 관리 — 다이어트로 저하된 면역력이나 구내염 예방을 위해 매일 챙겨 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>꾸준한 재구매 만족도 — 제품 품질에 만족하여 비타민이 떨어질 때마다 주기적으로 재구매함</t>
-        </is>
-      </c>
+          <t>훌륭한 가성비와 성분 — 유명 브랜드 제품 대비 가격이 저렴하고 성분이 양호함</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -5614,7 +5249,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5622,12 +5257,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대웅제약 맥주효모 비오틴 30정 30일분</t>
+          <t>닥터블릿 멜라드림 30정 30일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -5637,36 +5272,36 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000140&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=031930043&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/nz7SB5WS5Csy7uymMIBh600000140_00_00nz7SB5WS5Csy7uymMIBh.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260106/ifUNcDpBRic8ZZffJeay031930043_00_03ifUNcDpBRic8ZZffJeay.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>1561</v>
+        <v>1907</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>탈모 예방 및 모발 케어 — 머리숱이 휑해지거나 탈모 관리가 필요할 때 부담 없이 챙겨 먹기 좋음</t>
+          <t>숙면 유도에 도움 — 복용 후 수면 체류 및 숙면에 도움을 받음</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>지인 추천 기반 가성비 — 가격이 매우 저렴하고 품질이 우수하여 가족 및 지인 추천으로 많이 소비됨</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>부담 없는 꾸준한 복용성 — 정제 크기와 복용이 간편하여 장기적으로 자주 애용하게 됨</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>입문용 부담 없는 시도 — 다이소 소포장이라 첫 복용 시 시도하기 적합함</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>불명확한 개인별 효과 — 사람에 따라 체감 효과가 크지 않을 수 있음</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -5781,52 +5416,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>루테인/눈건강</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
         </is>
       </c>
     </row>
@@ -5838,52 +5473,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>CJ웰케어</t>
+          <t>유한양행</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>판티오</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>종근당</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>자연관</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>오브맘</t>
-        </is>
-      </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>영진약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>닥터블릿</t>
         </is>
       </c>
     </row>
@@ -5895,52 +5530,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
+          <t>대웅제약 마그네슘 샷 25ml x 5병 5일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>CJ 카무트 곡물과채콤부 화사 효소 10포 10일분</t>
+          <t>유한양행 장건강 생유산균 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 루테인 30정 30일분</t>
+          <t>[보령약국 X Pantio] [인교진 PICK] 다이어트 컷 올인원 15포 15일분</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>자연관 이지슬로 엑스트라버진 올리브오일＆레몬 4병</t>
+          <t>종근당 데일리와이즈 밀크씨슬 12정 12일분</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>오브맘 다이어트 홀릭 30포 15일분</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>올비텐 비타팡팡 30포</t>
+          <t>대웅제약 비타민C 30정 30일분</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>자연관 스파이크컷 바나바잎＆카테킨 4병</t>
+          <t>대웅제약 마그네슘 10정 10일분</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 혈당컷 다이어트 12정 12일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
+          <t>동국제약 이너케어＆유산균 30캡슐</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 맥주효모 비오틴 30정 30일분</t>
+          <t>닥터블릿 멜라드림 30정 30일분</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5586,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>4.8</v>
@@ -5963,22 +5598,22 @@
         <v>4.8</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="7">
@@ -5988,37 +5623,37 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2806</v>
+        <v>1451</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1264</v>
+        <v>1755</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>4149</v>
+        <v>261</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1131</v>
+        <v>318</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1060</v>
+        <v>6611</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>116</v>
+        <v>2837</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>359</v>
+        <v>752</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1409</v>
+        <v>7100</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>2833</v>
+        <v>2899</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1561</v>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -6026,115 +5661,92 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 가격 대비 성능 — 저렴한 가격으로 커피 대용 다이어트 음료를 즐길 수 있어 가성비가 높음
-거부감 없는 커피 대용 맛 — 일반 커피처럼 마시기 좋고 맛이 깔끔하여 일상 속 대체 음료로 적합함
-간편한 휴대 및 음용 방식 — 포 형태로 제작되어 어디서든 물에 타서 편하게 섭취 가능함</t>
+          <t>뛰어난 가성비 — 다이소 제품답게 매우 저렴한 가격에 구매 가능함
+액상 제형의 편의성과 맛 — 액체 타입이라 흡수가 잘 되며 맛도 양호함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>건강해지는 느낌과 좋은 맛 — 맛이 거북하지 않아 재구매하며 섭취 시 몸이 건강해지는 느낌을 받음
-중장년층 간편 건강 관리 — 50대 이후 필수 곡물 효소를 간편하게 보충할 수 있어 복용이 수월함</t>
+          <t>작아서 편한 캡슐 제형 — 캡슐 크기가 작아 목넘김이 편리함
+저렴한 가격과 알찬 구성 — 가성비가 뛰어나고 보관 용기의 밀폐력이 우수함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>극강의 부담 없는 가성비 — 저렴한 가격대로 매일 꾸준히 눈 건강을 관리할 수 있어 만족스러움
-운전 등 일상 섭취 편의 — 운전을 자주 하는 환경에서 복용이 간편하여 매일 챙겨 먹기 수월함
-빠른 배송 및 포장 만족 — 배송이 신속하게 이루어지고 제품 상태가 양호하여 신뢰도가 높음</t>
+          <t>하루 1포 간편 복용 — 1일 1포 섭취라 관리가 편함
+빠른 배송 서비스 — 배송이 빠름</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>꾸준한 건강 관리 재구매 — 올리브오일과 레몬즙 조합이 좋아 매번 꾸준하게 재구매하여 섭취함
-신선한 원료 배합 만족도 — 건강에 유익한 엑스트라버진 올리브오일과 레몬즙을 함께 간편히 마실 수 있음</t>
+          <t>부담 없는 저렴한 가격 — 저렴하게 밀크씨슬을 구매할 수 있음
+지속적인 건강 관리 도움 — 소포장으로 간편하게 구매하여 꾸준히 복용하기 적합함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>간식처럼 맛있는 다이어트 — 다이어트 보조제임에도 맛이 뛰어나 거부감 없이 자꾸 먹게 됨
-부담 없는 가성비와 접근성 — 올리브영 대비 저렴한 가격에 구매할 수 있어 필수 아이템으로 추천됨
-식단 시 심리적 안정감 — 식단 중 챙겨 먹는 것만으로도 체중 관리에 대한 심리적 만족을 제공함</t>
+          <t>착한 가격의 극강 가성비 — 한 달 분량 오메가3를 매우 저렴하게 구매할 수 있음
+말랑한 캡슐의 목넘김 — 캡슐이 말랑말랑하여 목에 걸리지 않음</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>아이들의 높은 기호도 — 아이가 질리지 않고 좋아하여 매일 비타민을 챙겨 먹이기에 아주 유용함
-톡톡 터지는 발포 식감 — 입안에서 슈팅스타처럼 팡팡 터지는 독특한 재미가 있어 먹는 즐거움이 큼
-뛰어난 품질과 가격 만족 — 5천 원이라는 저렴한 가격 대비 품질이 훌륭하여 다량 쟁여두고 먹임</t>
+          <t>뛰어난 가성비 — 가격 대비 품질이 좋아 무난하게 챙겨 먹기 적합함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>흡수 빠른 액상형 섭취 — 액상 형태로 되어 있어 흡수가 빠를 것 같고 하루 한 병 마시기 수월함
-식후 간편한 혈당 관리 — 식사 후 바로 섭취하여 건강 및 다이어트 관리에 심리적 도움을 받음</t>
+          <t>1,000원의 저렴한 소포장 — 10정 소포장이라 가격 부담 없이 테스트용으로 구매하기 좋음
+근육 뭉침 및 경련 완화 — 눈떨림이나 다리 경련, 근육 뭉침 증상 완화에 도움이 됨</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>식후 졸림 및 혈당 완화 — 식후 급격하게 찾아오던 식곤증과 혈당 스파이크 현상이 줄어드는 느낌임
-휴대성 높은 개별 소분 포장 — 작게 소분되어 있어 외출 시 가방에 챙겨 다니며 식후 복용하기 편함
-저렴한 가격의 높은 가성비 — 다이소 유통 제품답게 가격이 저렴하여 부담 없이 시도하기 좋음</t>
+          <t>피로 회복과 항산화 효과 — 복용 시 항산화 체계 관리 및 피로 회복에 도움을 줌
+약사 추천 극강 가성비 — 약사들도 추천할 만큼 가성비가 우수함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>압도적인 저렴한 가격대 — 기존 비타민C 제품 대비 가격이 매우 저렴하여 극강의 가성비를 자랑함
-간편한 일상 면역력 관리 — 다이어트로 저하된 면역력이나 구내염 예방을 위해 매일 챙겨 먹기 좋음
-꾸준한 재구매 만족도 — 제품 품질에 만족하여 비타민이 떨어질 때마다 주기적으로 재구매함</t>
+          <t>빠른 질 분비물 개선 효과 — 단기간 복용에도 질 분비물이 줄어드는 개선 효과를 체감함
+훌륭한 가성비와 성분 — 유명 브랜드 제품 대비 가격이 저렴하고 성분이 양호함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>탈모 예방 및 모발 케어 — 머리숱이 휑해지거나 탈모 관리가 필요할 때 부담 없이 챙겨 먹기 좋음
-지인 추천 기반 가성비 — 가격이 매우 저렴하고 품질이 우수하여 가족 및 지인 추천으로 많이 소비됨
-부담 없는 꾸준한 복용성 — 정제 크기와 복용이 간편하여 장기적으로 자주 애용하게 됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="90" customHeight="1">
+          <t>숙면 유도에 도움 — 복용 후 수면 체류 및 숙면에 도움을 받음
+입문용 부담 없는 시도 — 다이소 소포장이라 첫 복용 시 시도하기 적합함</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>즉각적인 체감 효과 미비 — 다이어트 효과가 즉각적으로 체감되지는 않아 지속적인 확인이 필요함</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>오프라인 구매의 불편함 — 시중 오프라인 매장에서 판매하는 곳이 적어 구매 접근성이 떨어짐
-적은 용량 구성의 아쉬움 — 10포 소용량으로 구성되어 30포 이상 대용량 제품을 원하는 아쉬움이 있음
-미미한 단기 효능 체감 — 복용 후 나타나는 소화 관련 효과가 강하게 느껴지지 않는다는 평이 있음</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>너무 강렬한 산미 부담 — 신맛이 지나치게 강해 마실 때마다 먹기 버거워하는 반응이 있음</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>즉각적인 감량 효과 미비 — 단기간 섭취로는 즉각적인 체중 감량 변화를 체감하기 어려움</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>단기 섭취 시 효과 불확실 — 단기간 복용으로는 체감 효과를 뚜렷하게 알기 어렵다는 의견이 있음
-평범한 체감 대비 가격 — 가격 대비 큰 체감 효과 없이 무난한 편이라는 평가가 존재함</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>체감 효과에 대한 아쉬움 — 기대하고 구매했으나 뚜렷한 변화를 느끼지 못해 평범하다는 반응이 있음</t>
-        </is>
-      </c>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>단기 체감 효과의 미흡 — 단기 복용으로는 다이어트 효과를 느끼기 어려움</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>표면 코팅제의 이질감 — 알약 표면의 코팅 느낌이 약간 강하게 느껴짐</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>불명확한 개인별 효과 — 사람에 따라 체감 효과가 크지 않을 수 있음</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -6144,42 +5756,42 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
           <t>2,000원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>1,000원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>2,000원</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -6843,729 +6455,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>플랫폼</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>순위</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>1위</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>2위</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>3위</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>4위</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>5위</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>6위</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>7위</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>8위</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>9위</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>10위</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="100" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>올리브영</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>썸네일</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>카테고리</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>세렌</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>히말라야</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>프로뉴트리션</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>생활약속</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>글로우뮤즈</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>딥트3일</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>푸드올로지</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>글로우뮤즈</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="46" customHeight="1">
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>상품명</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>[올영단독] 세렌 리스펙타 질 유산균 플러스 15캡슐 (15일분)</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>히말라야 숙취해소 파티스마트 츄 2개입 (베리/망고)</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>[피부건강] 글로우뮤즈 스킨 밸런스 파우더 레몬맛 14포 (14일분)</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>[딥트3일/남규리PICK]남규리의 바른 효소 리셋 8포</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>[올영단독] 지노마스터 질유산균 70캡슐 (70일분)</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>[속광콜라겐] 글로우뮤즈 올데이 글로우 콜라겐 복숭아 14포 (14일분)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>평점</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>리뷰수</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="n">
-        <v>425</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>27049</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>긍정리뷰</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>질과 장 듀얼 동시 케어 — 질 건강과 장 건강을 한 번에 더블케어할 수 있어 관리가 효율적임
-목넘김 편한 작은 캡슐 — 캡슐 크기가 작아 목에 걸리지 않고 아침에도 부담 없이 복용 가능함
-귀여운 포켓몬 카드케이스 — 자석형 카드케이스 굿즈가 동봉되어 언박싱의 재미와 실용성을 더함</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>원활한 배변 활동 및 디톡스 — 과식 후 섭취 시 화장실을 잘 가게 되어 더부룩했던 뱃살 관리에 도움됨
-단기 급찐급빠 체중 관리 — 여행 전후나 단기 다이어트 시 체중 감량 루틴으로 활용하기 유용함
-귀여운 캐릭터 콜라보 패키지 — 헬로키티 콜라보 패키지 등 디자인이 귀여워 섭취하는 만족감이 높음</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>40대 이너뷰티 관리 목적 — 이너뷰티와 일상 건강 관리를 위해 간편하게 챙겨 먹는 용도로 사용됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>부정리뷰</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>다소 큰 알약 크기 부담 — 프로 컷 정제의 알약 크기가 다소 커서 삼킬 때 부담스러울 수 있음</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>판매가</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>27,000원</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>990원</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>35,800원</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>16,200원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>27,400원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>26,800원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>11,400원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>59,000원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>17,900원</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>22,900원</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>링크</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:A11"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>카테고리</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>비율(%)</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>카카오선물하기</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>다이소몰</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>올리브영</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>12</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30</v>
-      </c>
-      <c r="D2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>10</v>
-      </c>
-      <c r="C3" t="n">
-        <v>25</v>
-      </c>
-      <c r="D3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>7</v>
-      </c>
-      <c r="C4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="D4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" t="n">
-        <v>10</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>홍삼/인삼</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>